--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121777315</v>
+        <v>121776845</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>57273</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,53 +2272,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615661</v>
+        <v>615623</v>
       </c>
       <c r="R16" t="n">
-        <v>6658549</v>
+        <v>6658637</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2347,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,29 +2363,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776885</v>
+        <v>121777315</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,41 +2393,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615640</v>
+        <v>615661</v>
       </c>
       <c r="R17" t="n">
-        <v>6658641</v>
+        <v>6658549</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2465,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2478,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,28 +2492,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778346</v>
+        <v>121778213</v>
       </c>
       <c r="B18" t="n">
-        <v>92039</v>
+        <v>78353</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2542,13 +2551,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615572</v>
+        <v>615582</v>
       </c>
       <c r="R18" t="n">
-        <v>6658467</v>
+        <v>6658483</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2577,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121776977</v>
+        <v>121777127</v>
       </c>
       <c r="B19" t="n">
-        <v>98113</v>
+        <v>94778</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,41 +2635,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615610</v>
+        <v>615583</v>
       </c>
       <c r="R19" t="n">
-        <v>6658537</v>
+        <v>6658588</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2689,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,12 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,22 +2723,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121776753</v>
+        <v>121777921</v>
       </c>
       <c r="B20" t="n">
-        <v>94778</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,21 +2751,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2771,13 +2775,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615442</v>
+        <v>615583</v>
       </c>
       <c r="R20" t="n">
-        <v>6658469</v>
+        <v>6658558</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2806,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777127</v>
+        <v>121776977</v>
       </c>
       <c r="B21" t="n">
-        <v>94778</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,41 +2859,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615583</v>
+        <v>615610</v>
       </c>
       <c r="R21" t="n">
-        <v>6658588</v>
+        <v>6658537</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2932,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,22 +2952,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121777921</v>
+        <v>121776885</v>
       </c>
       <c r="B22" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,41 +2976,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615583</v>
+        <v>615640</v>
       </c>
       <c r="R22" t="n">
-        <v>6658558</v>
+        <v>6658641</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3030,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,22 +3064,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121778217</v>
+        <v>121778346</v>
       </c>
       <c r="B23" t="n">
-        <v>94778</v>
+        <v>92039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,45 +3088,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615582</v>
+        <v>615572</v>
       </c>
       <c r="R23" t="n">
-        <v>6658483</v>
+        <v>6658467</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3146,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,12 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,7 +3170,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3189,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778322</v>
+        <v>121778217</v>
       </c>
       <c r="B24" t="n">
-        <v>91120</v>
+        <v>94778</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3201,25 +3200,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040162</v>
+        <v>2170</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3227,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615572</v>
+        <v>615582</v>
       </c>
       <c r="R24" t="n">
-        <v>6658467</v>
+        <v>6658483</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,12 +3277,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121778213</v>
+        <v>121778322</v>
       </c>
       <c r="B25" t="n">
-        <v>78353</v>
+        <v>91120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,37 +3326,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615582</v>
+        <v>615572</v>
       </c>
       <c r="R25" t="n">
-        <v>6658483</v>
+        <v>6658467</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3380,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3390,7 +3393,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,6 +3407,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3417,10 +3426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121776845</v>
+        <v>121776753</v>
       </c>
       <c r="B26" t="n">
-        <v>57273</v>
+        <v>94778</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3429,50 +3438,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100067</v>
+        <v>2170</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615623</v>
+        <v>615442</v>
       </c>
       <c r="R26" t="n">
-        <v>6658637</v>
+        <v>6658469</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,12 +3526,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2847,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121776977</v>
+        <v>121776885</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,38 +2859,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615610</v>
+        <v>615640</v>
       </c>
       <c r="R21" t="n">
-        <v>6658537</v>
+        <v>6658641</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,12 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121776885</v>
+        <v>121776977</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,38 +2971,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615640</v>
+        <v>615610</v>
       </c>
       <c r="R22" t="n">
-        <v>6658641</v>
+        <v>6658537</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3039,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3044,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778217</v>
+        <v>121778322</v>
       </c>
       <c r="B24" t="n">
-        <v>94778</v>
+        <v>91120</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,31 +3200,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3232,13 +3226,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615582</v>
+        <v>615572</v>
       </c>
       <c r="R24" t="n">
-        <v>6658483</v>
+        <v>6658467</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,12 +3271,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,51 +3304,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121778322</v>
+        <v>121776753</v>
       </c>
       <c r="B25" t="n">
-        <v>91120</v>
+        <v>94778</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040162</v>
+        <v>2170</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615572</v>
+        <v>615442</v>
       </c>
       <c r="R25" t="n">
-        <v>6658467</v>
+        <v>6658469</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3393,12 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,7 +3398,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3426,14 +3416,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121776753</v>
+        <v>121778217</v>
       </c>
       <c r="B26" t="n">
         <v>94778</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3460,16 +3450,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615442</v>
+        <v>615582</v>
       </c>
       <c r="R26" t="n">
-        <v>6658469</v>
+        <v>6658483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3495,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3505,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,6 +3519,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121776845</v>
+        <v>121778322</v>
       </c>
       <c r="B16" t="n">
-        <v>57273</v>
+        <v>91120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,46 +2276,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615623</v>
+        <v>615572</v>
       </c>
       <c r="R16" t="n">
-        <v>6658637</v>
+        <v>6658467</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,28 +2357,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121777315</v>
+        <v>121776885</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,53 +2388,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615661</v>
+        <v>615640</v>
       </c>
       <c r="R17" t="n">
-        <v>6658549</v>
+        <v>6658641</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2468,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,12 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,19 +2470,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2623,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777127</v>
+        <v>121777921</v>
       </c>
       <c r="B19" t="n">
-        <v>94778</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2616,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2666,10 +2643,10 @@
         <v>615583</v>
       </c>
       <c r="R19" t="n">
-        <v>6658588</v>
+        <v>6658558</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121777921</v>
+        <v>121777315</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,38 +2724,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615583</v>
+        <v>615661</v>
       </c>
       <c r="R20" t="n">
-        <v>6658558</v>
+        <v>6658549</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2810,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2809,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,28 +2823,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121776885</v>
+        <v>121778346</v>
       </c>
       <c r="B21" t="n">
-        <v>90728</v>
+        <v>92039</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,37 +2858,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615640</v>
+        <v>615572</v>
       </c>
       <c r="R21" t="n">
-        <v>6658641</v>
+        <v>6658467</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,7 +2917,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2927,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,22 +2942,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121776977</v>
+        <v>121777127</v>
       </c>
       <c r="B22" t="n">
-        <v>98113</v>
+        <v>94778</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,41 +2966,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615610</v>
+        <v>615583</v>
       </c>
       <c r="R22" t="n">
-        <v>6658537</v>
+        <v>6658588</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3034,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,12 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,22 +3054,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121778346</v>
+        <v>121776977</v>
       </c>
       <c r="B23" t="n">
-        <v>92039</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,41 +3078,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615572</v>
+        <v>615610</v>
       </c>
       <c r="R23" t="n">
-        <v>6658467</v>
+        <v>6658537</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3151,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3151,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,22 +3171,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778322</v>
+        <v>121776845</v>
       </c>
       <c r="B24" t="n">
-        <v>91120</v>
+        <v>57273</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,35 +3199,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040162</v>
+        <v>100067</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615572</v>
+        <v>615623</v>
       </c>
       <c r="R24" t="n">
-        <v>6658467</v>
+        <v>6658637</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,12 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,26 +3286,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121776753</v>
+        <v>121778217</v>
       </c>
       <c r="B25" t="n">
         <v>94778</v>
@@ -3338,16 +3338,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615442</v>
+        <v>615582</v>
       </c>
       <c r="R25" t="n">
-        <v>6658469</v>
+        <v>6658483</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3393,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,6 +3407,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3416,7 +3426,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121778217</v>
+        <v>121776753</v>
       </c>
       <c r="B26" t="n">
         <v>94778</v>
@@ -3450,20 +3460,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615582</v>
+        <v>615442</v>
       </c>
       <c r="R26" t="n">
-        <v>6658483</v>
+        <v>6658469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3495,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3505,12 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,7 +3520,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778322</v>
+        <v>121776977</v>
       </c>
       <c r="B16" t="n">
-        <v>91120</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,39 +2272,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615572</v>
+        <v>615610</v>
       </c>
       <c r="R16" t="n">
-        <v>6658467</v>
+        <v>6658537</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2345,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,29 +2359,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776885</v>
+        <v>121777127</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>94778</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,41 +2389,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615640</v>
+        <v>615583</v>
       </c>
       <c r="R17" t="n">
-        <v>6658641</v>
+        <v>6658588</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2477,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778213</v>
+        <v>121777315</v>
       </c>
       <c r="B18" t="n">
-        <v>78353</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,41 +2501,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615582</v>
+        <v>615661</v>
       </c>
       <c r="R18" t="n">
-        <v>6658483</v>
+        <v>6658549</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,28 +2600,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777921</v>
+        <v>121778322</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>91120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,38 +2631,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615583</v>
+        <v>615572</v>
       </c>
       <c r="R19" t="n">
-        <v>6658558</v>
+        <v>6658467</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2675,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2702,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,6 +2716,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121777315</v>
+        <v>121778213</v>
       </c>
       <c r="B20" t="n">
-        <v>98113</v>
+        <v>78353</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,53 +2747,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615661</v>
+        <v>615582</v>
       </c>
       <c r="R20" t="n">
-        <v>6658549</v>
+        <v>6658483</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,12 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,29 +2829,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121778346</v>
+        <v>121777921</v>
       </c>
       <c r="B21" t="n">
-        <v>92039</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,25 +2859,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R21" t="n">
-        <v>6658467</v>
+        <v>6658558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2917,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2927,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121777127</v>
+        <v>121776885</v>
       </c>
       <c r="B22" t="n">
-        <v>94778</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,41 +2971,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615583</v>
+        <v>615640</v>
       </c>
       <c r="R22" t="n">
-        <v>6658588</v>
+        <v>6658641</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,22 +3059,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121776977</v>
+        <v>121776845</v>
       </c>
       <c r="B23" t="n">
-        <v>98113</v>
+        <v>57273</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3078,41 +3083,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615610</v>
+        <v>615623</v>
       </c>
       <c r="R23" t="n">
-        <v>6658537</v>
+        <v>6658637</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3141,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,12 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121776845</v>
+        <v>121778346</v>
       </c>
       <c r="B24" t="n">
-        <v>57273</v>
+        <v>92039</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,46 +3208,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100067</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615623</v>
+        <v>615572</v>
       </c>
       <c r="R24" t="n">
-        <v>6658637</v>
+        <v>6658467</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,12 +3292,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121776977</v>
+        <v>121778346</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>92039</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,41 +2272,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615610</v>
+        <v>615572</v>
       </c>
       <c r="R16" t="n">
-        <v>6658537</v>
+        <v>6658467</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,12 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2360,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121777127</v>
+        <v>121776885</v>
       </c>
       <c r="B17" t="n">
-        <v>94778</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,41 +2384,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615583</v>
+        <v>615640</v>
       </c>
       <c r="R17" t="n">
-        <v>6658588</v>
+        <v>6658641</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,19 +2472,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121777315</v>
+        <v>121776977</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2522,32 +2517,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615661</v>
+        <v>615610</v>
       </c>
       <c r="R18" t="n">
-        <v>6658549</v>
+        <v>6658537</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2576,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,12 +2569,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,29 +2583,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121778322</v>
+        <v>121777127</v>
       </c>
       <c r="B19" t="n">
-        <v>91120</v>
+        <v>94778</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,39 +2613,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040162</v>
+        <v>2170</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R19" t="n">
-        <v>6658467</v>
+        <v>6658588</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2692,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,12 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,7 +2695,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2735,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121778213</v>
+        <v>121777315</v>
       </c>
       <c r="B20" t="n">
-        <v>78353</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,41 +2725,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615582</v>
+        <v>615661</v>
       </c>
       <c r="R20" t="n">
-        <v>6658483</v>
+        <v>6658549</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2810,7 +2800,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2810,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,28 +2824,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777921</v>
+        <v>121778213</v>
       </c>
       <c r="B21" t="n">
-        <v>90693</v>
+        <v>78353</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,25 +2855,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,13 +2883,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615583</v>
+        <v>615582</v>
       </c>
       <c r="R21" t="n">
-        <v>6658558</v>
+        <v>6658483</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121776885</v>
+        <v>121776845</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>57273</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,37 +2971,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615640</v>
+        <v>615623</v>
       </c>
       <c r="R22" t="n">
-        <v>6658641</v>
+        <v>6658637</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3034,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121776845</v>
+        <v>121778322</v>
       </c>
       <c r="B23" t="n">
-        <v>57273</v>
+        <v>91120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,46 +3092,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615623</v>
+        <v>615572</v>
       </c>
       <c r="R23" t="n">
-        <v>6658637</v>
+        <v>6658467</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3155,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3159,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,28 +3173,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778346</v>
+        <v>121777921</v>
       </c>
       <c r="B24" t="n">
-        <v>92039</v>
+        <v>90693</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R24" t="n">
-        <v>6658467</v>
+        <v>6658558</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778346</v>
+        <v>121778322</v>
       </c>
       <c r="B16" t="n">
-        <v>92039</v>
+        <v>91120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,24 +2276,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
@@ -2335,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,6 +2357,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2372,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776885</v>
+        <v>121776977</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,38 +2388,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615640</v>
+        <v>615610</v>
       </c>
       <c r="R17" t="n">
-        <v>6658641</v>
+        <v>6658537</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2447,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2461,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121776977</v>
+        <v>121776885</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,38 +2505,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615610</v>
+        <v>615640</v>
       </c>
       <c r="R18" t="n">
-        <v>6658537</v>
+        <v>6658641</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2559,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,12 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777127</v>
+        <v>121777921</v>
       </c>
       <c r="B19" t="n">
-        <v>94778</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,21 +2621,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2648,10 @@
         <v>615583</v>
       </c>
       <c r="R19" t="n">
-        <v>6658588</v>
+        <v>6658558</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121777315</v>
+        <v>121777127</v>
       </c>
       <c r="B20" t="n">
-        <v>98113</v>
+        <v>94778</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2725,53 +2729,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615661</v>
+        <v>615583</v>
       </c>
       <c r="R20" t="n">
-        <v>6658549</v>
+        <v>6658588</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2800,7 +2792,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,12 +2802,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,29 +2811,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121778213</v>
+        <v>121777315</v>
       </c>
       <c r="B21" t="n">
-        <v>78353</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,41 +2841,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615582</v>
+        <v>615661</v>
       </c>
       <c r="R21" t="n">
-        <v>6658483</v>
+        <v>6658549</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2918,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2926,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,18 +2940,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3076,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121778322</v>
+        <v>121778346</v>
       </c>
       <c r="B23" t="n">
-        <v>91120</v>
+        <v>92039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,22 +3096,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
@@ -3149,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,12 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,7 +3174,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121777921</v>
+        <v>121778213</v>
       </c>
       <c r="B24" t="n">
-        <v>90693</v>
+        <v>78353</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615583</v>
+        <v>615582</v>
       </c>
       <c r="R24" t="n">
-        <v>6658558</v>
+        <v>6658483</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778322</v>
+        <v>121776885</v>
       </c>
       <c r="B16" t="n">
-        <v>91120</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,35 +2276,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040162</v>
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615572</v>
+        <v>615640</v>
       </c>
       <c r="R16" t="n">
-        <v>6658467</v>
+        <v>6658641</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,29 +2354,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776977</v>
+        <v>121776845</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>57273</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,41 +2384,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615610</v>
+        <v>615623</v>
       </c>
       <c r="R17" t="n">
-        <v>6658537</v>
+        <v>6658637</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,12 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121776885</v>
+        <v>121778346</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>92039</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,37 +2509,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615640</v>
+        <v>615572</v>
       </c>
       <c r="R18" t="n">
-        <v>6658641</v>
+        <v>6658467</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2593,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777921</v>
+        <v>121778322</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>91120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,38 +2617,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615583</v>
+        <v>615572</v>
       </c>
       <c r="R19" t="n">
-        <v>6658558</v>
+        <v>6658467</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2680,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2688,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,6 +2702,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2959,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121776845</v>
+        <v>121778213</v>
       </c>
       <c r="B22" t="n">
-        <v>57273</v>
+        <v>78353</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,46 +2979,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100067</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615623</v>
+        <v>615582</v>
       </c>
       <c r="R22" t="n">
-        <v>6658637</v>
+        <v>6658483</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3043,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3048,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,22 +3063,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121778346</v>
+        <v>121776977</v>
       </c>
       <c r="B23" t="n">
-        <v>92039</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,41 +3087,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615572</v>
+        <v>615610</v>
       </c>
       <c r="R23" t="n">
-        <v>6658467</v>
+        <v>6658537</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3160,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3180,22 +3180,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778213</v>
+        <v>121777921</v>
       </c>
       <c r="B24" t="n">
-        <v>78353</v>
+        <v>90693</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615582</v>
+        <v>615583</v>
       </c>
       <c r="R24" t="n">
-        <v>6658483</v>
+        <v>6658558</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,7 +3304,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121778217</v>
+        <v>121776753</v>
       </c>
       <c r="B25" t="n">
         <v>94778</v>
@@ -3338,20 +3338,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615582</v>
+        <v>615442</v>
       </c>
       <c r="R25" t="n">
-        <v>6658483</v>
+        <v>6658469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3393,12 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,7 +3398,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3426,7 +3416,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121776753</v>
+        <v>121778217</v>
       </c>
       <c r="B26" t="n">
         <v>94778</v>
@@ -3460,16 +3450,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615442</v>
+        <v>615582</v>
       </c>
       <c r="R26" t="n">
-        <v>6658469</v>
+        <v>6658483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3495,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3505,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,6 +3519,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2605,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121778322</v>
+        <v>121777127</v>
       </c>
       <c r="B19" t="n">
-        <v>91120</v>
+        <v>94778</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,39 +2617,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040162</v>
+        <v>2170</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R19" t="n">
-        <v>6658467</v>
+        <v>6658588</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,12 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,7 +2699,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121777127</v>
+        <v>121778322</v>
       </c>
       <c r="B20" t="n">
-        <v>94778</v>
+        <v>91120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,41 +2729,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615583</v>
+        <v>615572</v>
       </c>
       <c r="R20" t="n">
-        <v>6658588</v>
+        <v>6658467</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2800,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,6 +2814,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121776885</v>
+        <v>121778346</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>92053</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,37 +2276,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615640</v>
+        <v>615572</v>
       </c>
       <c r="R16" t="n">
-        <v>6658641</v>
+        <v>6658467</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,22 +2360,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776845</v>
+        <v>121778213</v>
       </c>
       <c r="B17" t="n">
-        <v>57273</v>
+        <v>78366</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,46 +2388,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100067</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615623</v>
+        <v>615582</v>
       </c>
       <c r="R17" t="n">
-        <v>6658637</v>
+        <v>6658483</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2456,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,22 +2472,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778346</v>
+        <v>121776885</v>
       </c>
       <c r="B18" t="n">
-        <v>92039</v>
+        <v>90742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,37 +2500,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615572</v>
+        <v>615640</v>
       </c>
       <c r="R18" t="n">
-        <v>6658467</v>
+        <v>6658641</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,12 +2584,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2608,7 +2599,7 @@
         <v>121777127</v>
       </c>
       <c r="B19" t="n">
-        <v>94778</v>
+        <v>94796</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121778322</v>
+        <v>121776845</v>
       </c>
       <c r="B20" t="n">
-        <v>91120</v>
+        <v>57281</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,35 +2724,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040162</v>
+        <v>100067</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615572</v>
+        <v>615623</v>
       </c>
       <c r="R20" t="n">
-        <v>6658467</v>
+        <v>6658637</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,12 +2802,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,29 +2811,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777315</v>
+        <v>121777921</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>90707</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,50 +2841,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615661</v>
+        <v>615583</v>
       </c>
       <c r="R21" t="n">
-        <v>6658549</v>
+        <v>6658558</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2920,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,12 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,29 +2923,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121778213</v>
+        <v>121776977</v>
       </c>
       <c r="B22" t="n">
-        <v>78353</v>
+        <v>98131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,41 +2953,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615582</v>
+        <v>615610</v>
       </c>
       <c r="R22" t="n">
-        <v>6658483</v>
+        <v>6658537</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3038,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,7 +3026,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,22 +3046,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121776977</v>
+        <v>121777315</v>
       </c>
       <c r="B23" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,20 +3091,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615610</v>
+        <v>615661</v>
       </c>
       <c r="R23" t="n">
-        <v>6658537</v>
+        <v>6658549</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,12 +3155,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,28 +3169,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121777921</v>
+        <v>121778322</v>
       </c>
       <c r="B24" t="n">
-        <v>90693</v>
+        <v>91134</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,38 +3200,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615583</v>
+        <v>615572</v>
       </c>
       <c r="R24" t="n">
-        <v>6658558</v>
+        <v>6658467</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3271,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,6 +3285,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>121776753</v>
       </c>
       <c r="B25" t="n">
-        <v>94778</v>
+        <v>94796</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>121778217</v>
       </c>
       <c r="B26" t="n">
-        <v>94778</v>
+        <v>94796</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2263,7 +2263,7 @@
         <v>121778346</v>
       </c>
       <c r="B16" t="n">
-        <v>92053</v>
+        <v>92055</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121778213</v>
+        <v>121776885</v>
       </c>
       <c r="B17" t="n">
-        <v>78366</v>
+        <v>90744</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,37 +2388,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615582</v>
+        <v>615640</v>
       </c>
       <c r="R17" t="n">
-        <v>6658483</v>
+        <v>6658641</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,22 +2472,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121776885</v>
+        <v>121776845</v>
       </c>
       <c r="B18" t="n">
-        <v>90742</v>
+        <v>57281</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,37 +2500,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615640</v>
+        <v>615623</v>
       </c>
       <c r="R18" t="n">
-        <v>6658641</v>
+        <v>6658637</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,7 +2608,7 @@
         <v>121777127</v>
       </c>
       <c r="B19" t="n">
-        <v>94796</v>
+        <v>94798</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121776845</v>
+        <v>121776977</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
+        <v>98133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,50 +2729,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100067</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615623</v>
+        <v>615610</v>
       </c>
       <c r="R20" t="n">
-        <v>6658637</v>
+        <v>6658537</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,7 +2802,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,7 +2837,7 @@
         <v>121777921</v>
       </c>
       <c r="B21" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,10 +2946,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121776977</v>
+        <v>121777315</v>
       </c>
       <c r="B22" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,20 +2979,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615610</v>
+        <v>615661</v>
       </c>
       <c r="R22" t="n">
-        <v>6658537</v>
+        <v>6658549</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,7 +3033,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,12 +3043,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,28 +3057,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121777315</v>
+        <v>121778322</v>
       </c>
       <c r="B23" t="n">
-        <v>98131</v>
+        <v>91136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,50 +3088,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615661</v>
+        <v>615572</v>
       </c>
       <c r="R23" t="n">
-        <v>6658549</v>
+        <v>6658467</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3145,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,12 +3159,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,22 +3180,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778322</v>
+        <v>121778213</v>
       </c>
       <c r="B24" t="n">
-        <v>91134</v>
+        <v>78368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,35 +3208,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040162</v>
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615572</v>
+        <v>615582</v>
       </c>
       <c r="R24" t="n">
-        <v>6658467</v>
+        <v>6658483</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,12 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,7 +3286,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121776753</v>
+        <v>121778217</v>
       </c>
       <c r="B25" t="n">
-        <v>94796</v>
+        <v>94798</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,16 +3338,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615442</v>
+        <v>615582</v>
       </c>
       <c r="R25" t="n">
-        <v>6658469</v>
+        <v>6658483</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3393,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,6 +3407,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3416,10 +3426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121778217</v>
+        <v>121776753</v>
       </c>
       <c r="B26" t="n">
-        <v>94796</v>
+        <v>94798</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3450,20 +3460,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615582</v>
+        <v>615442</v>
       </c>
       <c r="R26" t="n">
-        <v>6658483</v>
+        <v>6658469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3495,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3505,12 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,7 +3520,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121778346</v>
+        <v>121777921</v>
       </c>
       <c r="B16" t="n">
-        <v>92055</v>
+        <v>90710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R16" t="n">
-        <v>6658467</v>
+        <v>6658558</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121776885</v>
+        <v>121778322</v>
       </c>
       <c r="B17" t="n">
-        <v>90744</v>
+        <v>91137</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,37 +2388,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615640</v>
+        <v>615572</v>
       </c>
       <c r="R17" t="n">
-        <v>6658641</v>
+        <v>6658467</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2455,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,28 +2469,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121776845</v>
+        <v>121778346</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
+        <v>92056</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,46 +2504,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100067</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615623</v>
+        <v>615572</v>
       </c>
       <c r="R18" t="n">
-        <v>6658637</v>
+        <v>6658467</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2588,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121777127</v>
+        <v>121776885</v>
       </c>
       <c r="B19" t="n">
-        <v>94798</v>
+        <v>90745</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,41 +2612,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615583</v>
+        <v>615640</v>
       </c>
       <c r="R19" t="n">
-        <v>6658588</v>
+        <v>6658641</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121776977</v>
+        <v>121778213</v>
       </c>
       <c r="B20" t="n">
-        <v>98133</v>
+        <v>78369</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,41 +2724,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615610</v>
+        <v>615582</v>
       </c>
       <c r="R20" t="n">
-        <v>6658537</v>
+        <v>6658483</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2792,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,12 +2797,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,22 +2812,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777921</v>
+        <v>121777315</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>98140</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,38 +2836,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615583</v>
+        <v>615661</v>
       </c>
       <c r="R21" t="n">
-        <v>6658558</v>
+        <v>6658549</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2909,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,7 +2921,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,28 +2935,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121777315</v>
+        <v>121777127</v>
       </c>
       <c r="B22" t="n">
-        <v>98133</v>
+        <v>94805</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,53 +2966,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615661</v>
+        <v>615583</v>
       </c>
       <c r="R22" t="n">
-        <v>6658549</v>
+        <v>6658588</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3043,12 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,29 +3048,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121778322</v>
+        <v>121776977</v>
       </c>
       <c r="B23" t="n">
-        <v>91136</v>
+        <v>98140</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,39 +3078,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615572</v>
+        <v>615610</v>
       </c>
       <c r="R23" t="n">
-        <v>6658467</v>
+        <v>6658537</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,12 +3151,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På låga av tall</t>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,29 +3165,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121778213</v>
+        <v>121776845</v>
       </c>
       <c r="B24" t="n">
-        <v>78368</v>
+        <v>57281</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,37 +3199,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100067</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615582</v>
+        <v>615623</v>
       </c>
       <c r="R24" t="n">
-        <v>6658483</v>
+        <v>6658637</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,12 +3292,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
         <v>121778217</v>
       </c>
       <c r="B25" t="n">
-        <v>94798</v>
+        <v>94805</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>121776753</v>
       </c>
       <c r="B26" t="n">
-        <v>94798</v>
+        <v>94805</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 55284-2024 artfynd.xlsx
+++ b/artfynd/A 55284-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121777921</v>
+        <v>121778322</v>
       </c>
       <c r="B16" t="n">
-        <v>90710</v>
+        <v>91146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,38 +2272,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615583</v>
+        <v>615572</v>
       </c>
       <c r="R16" t="n">
-        <v>6658558</v>
+        <v>6658467</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2335,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På låga av tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,6 +2357,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2372,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121778322</v>
+        <v>121777127</v>
       </c>
       <c r="B17" t="n">
-        <v>91137</v>
+        <v>94814</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,39 +2388,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040162</v>
+        <v>2170</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R17" t="n">
-        <v>6658467</v>
+        <v>6658588</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,12 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På låga av tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2470,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121778346</v>
+        <v>121777921</v>
       </c>
       <c r="B18" t="n">
-        <v>92056</v>
+        <v>90719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,25 +2500,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615572</v>
+        <v>615583</v>
       </c>
       <c r="R18" t="n">
-        <v>6658467</v>
+        <v>6658558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121776885</v>
+        <v>121778346</v>
       </c>
       <c r="B19" t="n">
-        <v>90745</v>
+        <v>92065</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,37 +2616,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615640</v>
+        <v>615572</v>
       </c>
       <c r="R19" t="n">
-        <v>6658641</v>
+        <v>6658467</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121778213</v>
+        <v>121776977</v>
       </c>
       <c r="B20" t="n">
-        <v>78369</v>
+        <v>98149</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,41 +2724,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Mossbosjön, Mossbosjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615582</v>
+        <v>615610</v>
       </c>
       <c r="R20" t="n">
-        <v>6658483</v>
+        <v>6658537</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,7 +2797,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Utanför Uppsala universitets provyta</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,22 +2817,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121777315</v>
+        <v>121778213</v>
       </c>
       <c r="B21" t="n">
-        <v>98140</v>
+        <v>78376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,53 +2841,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Råksjön söder om, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615661</v>
+        <v>615582</v>
       </c>
       <c r="R21" t="n">
-        <v>6658549</v>
+        <v>6658483</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,12 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,29 +2923,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121777127</v>
+        <v>121776885</v>
       </c>
       <c r="B22" t="n">
-        <v>94805</v>
+        <v>90754</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,41 +2953,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615583</v>
+        <v>615640</v>
       </c>
       <c r="R22" t="n">
-        <v>6658588</v>
+        <v>6658641</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3029,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,22 +3041,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121776977</v>
+        <v>121776845</v>
       </c>
       <c r="B23" t="n">
-        <v>98140</v>
+        <v>57285</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3078,41 +3065,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mossbosjön, Mossbosjön, Upl</t>
+          <t>Vilvallen, Vilvallen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615610</v>
+        <v>615623</v>
       </c>
       <c r="R23" t="n">
-        <v>6658537</v>
+        <v>6658637</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3141,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,12 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Utanför Uppsala universitets provyta</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121776845</v>
+        <v>121777315</v>
       </c>
       <c r="B24" t="n">
-        <v>57281</v>
+        <v>98149</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3195,50 +3186,53 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100067</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vilvallen, Vilvallen, Upl</t>
+          <t>Råksjön söder om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615623</v>
+        <v>615661</v>
       </c>
       <c r="R24" t="n">
-        <v>6658637</v>
+        <v>6658549</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3271,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Markerade med försökskäppar inom yta som ska trakthuggas, markberedas och planteras.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,28 +3285,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121778217</v>
+        <v>121776753</v>
       </c>
       <c r="B25" t="n">
-        <v>94805</v>
+        <v>94814</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,20 +3338,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615582</v>
+        <v>615442</v>
       </c>
       <c r="R25" t="n">
-        <v>6658483</v>
+        <v>6658469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3393,12 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,7 +3398,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3426,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121776753</v>
+        <v>121778217</v>
       </c>
       <c r="B26" t="n">
-        <v>94805</v>
+        <v>94814</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,16 +3450,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615442</v>
+        <v>615582</v>
       </c>
       <c r="R26" t="n">
-        <v>6658469</v>
+        <v>6658483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3495,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3505,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad stubbe tillsammans med mörk kolflarnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,6 +3519,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
